--- a/data/raw/legal_corpus/manifest/labor/document_manifest.xlsx
+++ b/data/raw/legal_corpus/manifest/labor/document_manifest.xlsx
@@ -538,7 +538,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DOC_08</t>
+          <t>DOC_LABOR_08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DOC_09</t>
+          <t>DOC_LABOR_09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DOC_10</t>
+          <t>DOC_LABOR_10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DOC_11</t>
+          <t>DOC_LABOR_11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
